--- a/web/public/forms/wih-seonggwa.xlsx
+++ b/web/public/forms/wih-seonggwa.xlsx
@@ -1004,7 +1004,7 @@
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 괄리기간</t>
+          <t xml:space="preserve"> 관리기간</t>
         </is>
       </c>
       <c r="B6" s="5" t="n"/>

--- a/web/public/forms/wih-seonggwa.xlsx
+++ b/web/public/forms/wih-seonggwa.xlsx
@@ -644,7 +644,7 @@
     <row r="1" ht="18" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com   무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com   건설 서식</t>
         </is>
       </c>
       <c r="AS1" s="2" t="inlineStr">

--- a/web/public/forms/wih-seonggwa.xlsx
+++ b/web/public/forms/wih-seonggwa.xlsx
@@ -644,7 +644,7 @@
     <row r="1" ht="18" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com   건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com   무료 건설 서식</t>
         </is>
       </c>
       <c r="AS1" s="2" t="inlineStr">
